--- a/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Yield Per Hectare - Major Commercial Crops.xlsx
+++ b/data/publications/handbook-statistics-on-indian-economy/annual-series/output-and-prices/Yield Per Hectare - Major Commercial Crops.xlsx
@@ -8,7 +8,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>Year</t>
   </si>
@@ -283,13 +283,10 @@
     <t>Kg / Hectare</t>
   </si>
   <si>
-    <t xml:space="preserve">Notes : 1. Data for 2025-26   are based on First Advance Estimates.
-            2. Data for 1950-51 to 1969-70 relate to total of five major oilseeds,viz., groundnut,  castorseed, sesamum, rapeseed and mustard, and linseed.
-            3. Data for 1950-51 and 1951-52 relate to Jute crop only.
-            4. Oilseed data comprises total for nine oilseeds out of the eleven in all.
-            5. - : Not Available.
-Also see Notes on Tables.
-Source :  Ministry of Agriculture &amp; Farmers Welfare, Government of India.</t>
+    <t xml:space="preserve">Notes   : 1. Data for 2025-26 are based on Third Advance Estimates.
+               2. - : Not Available.
+                   Also see Notes on Tables.
+Source : Ministry of Agriculture &amp; Farmers Welfare, Government of India, Coffee Board of India, Tea Board of India.</t>
   </si>
 </sst>
 </file>
@@ -516,12 +513,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L86"/>
+  <dimension ref="A1:M87"/>
   <cols>
     <col min="1" max="1" width="4.67767866666667" customWidth="1"/>
     <col min="2" max="2" width="14.701508" customWidth="1"/>
     <col min="3" max="12" width="12.5491986666667" customWidth="1"/>
     <col min="13" max="13" width="86736e-6" customWidth="1"/>
+    <col min="14" max="14" width="4.67767866666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
@@ -638,31 +636,31 @@
         <v>12</v>
       </c>
       <c r="C9" s="9">
-        <v>2350</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>13</v>
+        <v>2228</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1460</v>
       </c>
       <c r="E9" s="9">
-        <v>1155</v>
+        <v>1017</v>
       </c>
       <c r="F9" s="9">
-        <v>1442</v>
+        <v>1394</v>
       </c>
       <c r="G9" s="9">
-        <v>83537</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="I9" s="9" t="s">
-        <v>13</v>
+        <v>84987</v>
+      </c>
+      <c r="H9" s="9">
+        <v>2176</v>
+      </c>
+      <c r="I9" s="9">
+        <v>825</v>
       </c>
       <c r="J9" s="9">
-        <v>448</v>
+        <v>428</v>
       </c>
       <c r="K9" s="9">
-        <v>2749</v>
+        <v>2793</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>13</v>
@@ -688,7 +686,7 @@
         <v>83416</v>
       </c>
       <c r="H10" s="10">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="I10" s="10">
         <v>815</v>
@@ -3294,7 +3292,7 @@
       </c>
     </row>
     <row r="85" s="1" customFormat="1" ht="14.3991" customHeight="1"/>
-    <row r="86" s="1" customFormat="1" ht="91.7276" customHeight="1">
+    <row r="86" s="1" customFormat="1" ht="101.8603" customHeight="1">
       <c r="B86" s="15" t="s">
         <v>91</v>
       </c>
@@ -3310,6 +3308,7 @@
       <c r="L86" s="15"/>
       <c r="M86" s="15"/>
     </row>
+    <row r="87" s="1" customFormat="1" ht="28.7982" customHeight="1"/>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B2:M2"/>
